--- a/quiz.xlsx
+++ b/quiz.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="111">
   <si>
     <t>問題</t>
   </si>
@@ -126,6 +126,222 @@
   </si>
   <si>
     <t>茨城大学</t>
+  </si>
+  <si>
+    <t>附属中学校の校歌を作曲した人物は誰？</t>
+  </si>
+  <si>
+    <t>滝廉太郎</t>
+  </si>
+  <si>
+    <t>山田耕筰</t>
+  </si>
+  <si>
+    <t>中田喜直</t>
+  </si>
+  <si>
+    <t>團伊玖磨</t>
+  </si>
+  <si>
+    <t>附属中学校の校歌を作詞した人物は誰？</t>
+  </si>
+  <si>
+    <t>勝承夫</t>
+  </si>
+  <si>
+    <t>北原白秋</t>
+  </si>
+  <si>
+    <t>野口雨情</t>
+  </si>
+  <si>
+    <t>西條八十</t>
+  </si>
+  <si>
+    <t>附属中学校の校歌が制定されたのはいつ？</t>
+  </si>
+  <si>
+    <t>1963年</t>
+  </si>
+  <si>
+    <t>1965年</t>
+  </si>
+  <si>
+    <t>1968年</t>
+  </si>
+  <si>
+    <t>1970年</t>
+  </si>
+  <si>
+    <t>現在の茨城大学教育学部附属中学校が発足したのはいつ？</t>
+  </si>
+  <si>
+    <t>1947年</t>
+  </si>
+  <si>
+    <t>1958年</t>
+  </si>
+  <si>
+    <t>1978年</t>
+  </si>
+  <si>
+    <t>附属中学校の前身の一つではないものは？</t>
+  </si>
+  <si>
+    <t>附属水城小中学校</t>
+  </si>
+  <si>
+    <t>附属愛宕小中学校</t>
+  </si>
+  <si>
+    <t>附属常磐小中学校</t>
+  </si>
+  <si>
+    <t>どちらも前身である</t>
+  </si>
+  <si>
+    <t>附属中学校が現在地に発足したのは何年？</t>
+  </si>
+  <si>
+    <t>1955年</t>
+  </si>
+  <si>
+    <t>1961年</t>
+  </si>
+  <si>
+    <t>旧4号館</t>
+  </si>
+  <si>
+    <t>旧5号館</t>
+  </si>
+  <si>
+    <t>旧6号館</t>
+  </si>
+  <si>
+    <t>旧7号館</t>
+  </si>
+  <si>
+    <t>附属中学校の前身となる男子師範学校附属小学校が開校したのはいつ？</t>
+  </si>
+  <si>
+    <t>明治5年</t>
+  </si>
+  <si>
+    <t>明治10年</t>
+  </si>
+  <si>
+    <t>明治15年</t>
+  </si>
+  <si>
+    <t>明治20年</t>
+  </si>
+  <si>
+    <t>校歌の歌詞に登場する川はどれ？</t>
+  </si>
+  <si>
+    <t>利根川</t>
+  </si>
+  <si>
+    <t>久慈川</t>
+  </si>
+  <si>
+    <t>那珂川</t>
+  </si>
+  <si>
+    <t>鬼怒川</t>
+  </si>
+  <si>
+    <t>校歌の歌詞に登場する山並みはどれ？</t>
+  </si>
+  <si>
+    <t>筑波山</t>
+  </si>
+  <si>
+    <t>八溝山</t>
+  </si>
+  <si>
+    <t>那須の山なみ</t>
+  </si>
+  <si>
+    <t>阿武隈高地</t>
+  </si>
+  <si>
+    <t>校歌の一節「われらこそ ○○ の初花」に入る言葉は？</t>
+  </si>
+  <si>
+    <t>常陸</t>
+  </si>
+  <si>
+    <t>水戸</t>
+  </si>
+  <si>
+    <t>茨城</t>
+  </si>
+  <si>
+    <t>学び</t>
+  </si>
+  <si>
+    <t>附属中学校が本年度迎えた統合何周年として紹介されている？</t>
+  </si>
+  <si>
+    <t>52周年</t>
+  </si>
+  <si>
+    <t>55周年</t>
+  </si>
+  <si>
+    <t>57周年</t>
+  </si>
+  <si>
+    <t>60周年</t>
+  </si>
+  <si>
+    <t>改修され「ものづくり棟」として生まれ変わった建物は？</t>
+  </si>
+  <si>
+    <t>附属中学校では「総合的な学習の時間」を何と呼んでいる？</t>
+  </si>
+  <si>
+    <t>グローバル社会科</t>
+  </si>
+  <si>
+    <t>グローバル市民科</t>
+  </si>
+  <si>
+    <t>グローバル探究科</t>
+  </si>
+  <si>
+    <t>グローバル学習科</t>
+  </si>
+  <si>
+    <t>附属中学校で行われるスポーツフェスティバルは年間何回開催される？</t>
+  </si>
+  <si>
+    <t>1回</t>
+  </si>
+  <si>
+    <t>2回</t>
+  </si>
+  <si>
+    <t>3回</t>
+  </si>
+  <si>
+    <t>4回</t>
+  </si>
+  <si>
+    <t>パソコン部にある最先端機械のうち正しくないのはどれ？</t>
+  </si>
+  <si>
+    <t>3Dプリンター</t>
+  </si>
+  <si>
+    <t>VRゴーグル</t>
+  </si>
+  <si>
+    <t>8Kテレビ</t>
+  </si>
+  <si>
+    <t>ドローン</t>
   </si>
 </sst>
 </file>
@@ -502,7 +718,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23FD2BB2-1846-6C45-A06C-853CC1AFF26A}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
@@ -625,6 +841,306 @@
         <v>1</v>
       </c>
     </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" t="s">
+        <v>44</v>
+      </c>
+      <c r="F9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>87</v>
+      </c>
+      <c r="B13" t="s">
+        <v>88</v>
+      </c>
+      <c r="C13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D13" t="s">
+        <v>90</v>
+      </c>
+      <c r="E13" t="s">
+        <v>91</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>92</v>
+      </c>
+      <c r="B14" t="s">
+        <v>93</v>
+      </c>
+      <c r="C14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D14" t="s">
+        <v>95</v>
+      </c>
+      <c r="E14" t="s">
+        <v>96</v>
+      </c>
+      <c r="F14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>97</v>
+      </c>
+      <c r="B15" t="s">
+        <v>98</v>
+      </c>
+      <c r="C15" t="s">
+        <v>99</v>
+      </c>
+      <c r="D15" t="s">
+        <v>100</v>
+      </c>
+      <c r="E15" t="s">
+        <v>101</v>
+      </c>
+      <c r="F15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" t="s">
+        <v>58</v>
+      </c>
+      <c r="D16" t="s">
+        <v>59</v>
+      </c>
+      <c r="E16" t="s">
+        <v>60</v>
+      </c>
+      <c r="F16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>61</v>
+      </c>
+      <c r="B17" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17" t="s">
+        <v>63</v>
+      </c>
+      <c r="D17" t="s">
+        <v>64</v>
+      </c>
+      <c r="E17" t="s">
+        <v>65</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>66</v>
+      </c>
+      <c r="B18" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18" t="s">
+        <v>69</v>
+      </c>
+      <c r="E18" t="s">
+        <v>70</v>
+      </c>
+      <c r="F18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>71</v>
+      </c>
+      <c r="B19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19" t="s">
+        <v>74</v>
+      </c>
+      <c r="E19" t="s">
+        <v>75</v>
+      </c>
+      <c r="F19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>76</v>
+      </c>
+      <c r="B20" t="s">
+        <v>77</v>
+      </c>
+      <c r="C20" t="s">
+        <v>78</v>
+      </c>
+      <c r="D20" t="s">
+        <v>79</v>
+      </c>
+      <c r="E20" t="s">
+        <v>80</v>
+      </c>
+      <c r="F20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>81</v>
+      </c>
+      <c r="B21" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D21" t="s">
+        <v>84</v>
+      </c>
+      <c r="E21" t="s">
+        <v>85</v>
+      </c>
+      <c r="F21">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
